--- a/test/gCOP.xlsx
+++ b/test/gCOP.xlsx
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wolfgang\Documents\GitHub\SACOBRA_Py\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D8F39A-C5AD-421B-9755-B239AD761089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844A0CFA-EA69-46B8-91E8-7CA9E1167211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="384" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>name</t>
   </si>
@@ -42,9 +51,6 @@
     <t>sDim</t>
   </si>
   <si>
-    <t>maxViol</t>
-  </si>
-  <si>
     <t>G01</t>
   </si>
   <si>
@@ -118,6 +124,24 @@
   </si>
   <si>
     <t>Gxx: problems with equality constraints</t>
+  </si>
+  <si>
+    <t>maxViol_e4</t>
+  </si>
+  <si>
+    <t>maxViol_e7</t>
+  </si>
+  <si>
+    <t>fbest_e4</t>
+  </si>
+  <si>
+    <t>fbest_e7</t>
+  </si>
+  <si>
+    <t>_e4: GCOP(…, mu=1e-4)</t>
+  </si>
+  <si>
+    <t>_e7: GCOP(…, mu=1e-7)</t>
   </si>
 </sst>
 </file>
@@ -125,7 +149,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000000E+00"/>
+    <numFmt numFmtId="166" formatCode="0.0000E+00"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -191,11 +215,11 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -476,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:G30"/>
+  <dimension ref="C1:J30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="6.21875" customWidth="1"/>
@@ -484,37 +508,57 @@
     <col min="5" max="5" width="5.5546875" customWidth="1"/>
     <col min="6" max="6" width="5.44140625" customWidth="1"/>
     <col min="7" max="7" width="14.44140625" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
+    <row r="1" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
-        <v>5</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -525,13 +569,22 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>-15</v>
+      </c>
+      <c r="J5">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -542,30 +595,48 @@
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>-0.74731000000000003</v>
+      </c>
+      <c r="J6">
+        <v>-0.74731000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>-1</v>
+      </c>
+      <c r="J7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
         <v>7</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C8" t="s">
-        <v>8</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -576,30 +647,48 @@
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C9" s="5" t="s">
-        <v>9</v>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>-30665.538671999999</v>
+      </c>
+      <c r="J8">
+        <v>-30665.538671999999</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D9">
         <v>5</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>3</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="5">
         <v>2.2737369999999998E-13</v>
       </c>
-    </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="H9" s="5">
+        <v>2.2737369999999998E-13</v>
+      </c>
+      <c r="I9">
+        <v>5126.4981100000005</v>
+      </c>
+      <c r="J9">
+        <v>5126.4981100000005</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -610,13 +699,22 @@
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>-6961.8138760000002</v>
+      </c>
+      <c r="J10">
+        <v>-6961.8138760000002</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -627,13 +725,22 @@
       <c r="F11">
         <v>1</v>
       </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>24.306208999999999</v>
+      </c>
+      <c r="J11">
+        <v>24.306208999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -644,13 +751,22 @@
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>-9.5824999999999994E-2</v>
+      </c>
+      <c r="J12">
+        <v>-9.5824999999999994E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -661,13 +777,22 @@
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>680.63005699999997</v>
+      </c>
+      <c r="J13">
+        <v>680.63005699999997</v>
+      </c>
+    </row>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -678,98 +803,152 @@
       <c r="F14">
         <v>1</v>
       </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C15" s="5" t="s">
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>7049.2480219999998</v>
+      </c>
+      <c r="J14">
+        <v>7049.2480219999998</v>
+      </c>
+    </row>
+    <row r="15" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1.110223E-16</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1.110223E-16</v>
+      </c>
+      <c r="I15">
+        <v>0.75</v>
+      </c>
+      <c r="J15">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
         <v>15</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1.110223E-16</v>
-      </c>
-    </row>
-    <row r="16" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>-1</v>
+      </c>
+      <c r="J16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C17" s="5" t="s">
-        <v>17</v>
       </c>
       <c r="D17">
         <v>3</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>3</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="5">
         <v>1.2183020000000001E-7</v>
       </c>
-    </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C18" s="5" t="s">
-        <v>18</v>
+      <c r="H17" s="5">
+        <v>1.2183020000000001E-7</v>
+      </c>
+      <c r="I17">
+        <v>5.3949999999999998E-2</v>
+      </c>
+      <c r="J17">
+        <v>5.3949999999999998E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>3</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="5">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C19" s="5" t="s">
-        <v>19</v>
+      <c r="H18" s="5">
+        <v>1.403744E-9</v>
+      </c>
+      <c r="I18">
+        <v>-47.764887999999999</v>
+      </c>
+      <c r="J18">
+        <v>-47.761091</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>2</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="5">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="H19" s="5">
+        <v>9.6477489999999998E-11</v>
+      </c>
+      <c r="I19">
+        <v>961.71502199999998</v>
+      </c>
+      <c r="J19">
+        <v>961.71517200000005</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20">
         <v>38</v>
@@ -780,30 +959,48 @@
       <c r="F20">
         <v>1</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="5">
         <v>5.0937029999999999E-6</v>
       </c>
-    </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C21" s="5" t="s">
-        <v>21</v>
+      <c r="H20" s="5">
+        <v>5.0937029999999999E-6</v>
+      </c>
+      <c r="I20">
+        <v>-1.9051549999999999</v>
+      </c>
+      <c r="J20">
+        <v>-1.9051549999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>4</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="5">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="H21" s="5">
+        <v>1.7751060000000001E-9</v>
+      </c>
+      <c r="I21">
+        <v>8853.5340159999996</v>
+      </c>
+      <c r="J21">
+        <v>8853.5399010000001</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22">
         <v>13</v>
@@ -814,13 +1011,22 @@
       <c r="F22">
         <v>1</v>
       </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>-0.86602500000000004</v>
+      </c>
+      <c r="J22">
+        <v>-0.86602500000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -831,64 +1037,100 @@
       <c r="F23">
         <v>1</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="5">
         <v>1.5099030000000001E-14</v>
       </c>
-    </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C24" s="5" t="s">
-        <v>24</v>
+      <c r="H23" s="5">
+        <v>1.5099030000000001E-14</v>
+      </c>
+      <c r="I23">
+        <v>32.655593000000003</v>
+      </c>
+      <c r="J23">
+        <v>32.655593000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="D24">
         <v>6</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="4">
         <v>5</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="5">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C25" s="5" t="s">
-        <v>25</v>
+      <c r="H24" s="5">
+        <v>2.2737369999999998E-13</v>
+      </c>
+      <c r="I24">
+        <v>193.72451000000001</v>
+      </c>
+      <c r="J24">
+        <v>193.786925</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="D25">
         <v>20</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>19</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
-      <c r="G25" s="1">
-        <v>9.5923080000000002E-5</v>
-      </c>
-    </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C26" s="5" t="s">
-        <v>26</v>
+      <c r="G25" s="5">
+        <v>9.2364850000000004E-5</v>
+      </c>
+      <c r="H25" s="5">
+        <v>3.7020070000000002E-7</v>
+      </c>
+      <c r="I25">
+        <v>236.34093999999999</v>
+      </c>
+      <c r="J25">
+        <v>236.37031400000001</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="D26">
         <v>6</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>4</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="G26" s="5">
+        <v>3.4849609999999999E-8</v>
+      </c>
+      <c r="H26" s="5">
+        <v>3.4849609999999999E-8</v>
+      </c>
+      <c r="I26">
+        <v>-400.00000599999998</v>
+      </c>
+      <c r="J26">
+        <v>-400.00000599999998</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -899,13 +1141,22 @@
       <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C30" s="5" t="s">
-        <v>29</v>
+      <c r="G27" s="5">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>-5.508013</v>
+      </c>
+      <c r="J27">
+        <v>-5.508013</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
